--- a/tests/realSuite/Piano-Viaggi_Gioco-Volley_8-gennaio-2026_4-DEF_con-vettore-ed-integrazione/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_Gioco-Volley_8-gennaio-2026_4-DEF_con-vettore-ed-integrazione/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,37 +531,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>STENICO, Via Risorgimento 11/A</t>
+          <t>FIAVE', Via De Gasperi 23</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC GIUDICARIE ESTERIORI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MEZZOLOMBARDO, via S. Francesco di fronte fermata Stazione FS</t>
+          <t>STENICO, Via Risorgimento 11/A</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC RIVA 1</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NAGO, Via di Tezze 4 - fermata bus</t>
+          <t>MEZZOLOMBARDO, via S. Francesco di fronte fermata Stazione FS</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -571,120 +571,135 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC RIVA 2</t>
+          <t>IC RIVA 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RIVA DEL GARDA, Via Grez 7/F (Plesso Primaria Zadra)</t>
+          <t>NAGO, Via di Tezze 4 - fermata bus</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC ROVERETO NORD</t>
+          <t>IC RIVA 2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ROVERETO, Fermata Bus Viale Trento, bivio Brione</t>
+          <t>RIVA DEL GARDA, Via Grez 7/F (Plesso Primaria Zadra)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC TAIO</t>
+          <t>IC ROVERETO NORD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TRES, Scuola Primaria</t>
+          <t>ROVERETO, Fermata Bus Viale Trento, bivio Brione</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IC TAIO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BONDO, Via Indipendenza, 105</t>
+          <t>TRES, Scuola Primaria</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC TRENTO 3</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TRENTO, Fermata Arcate Gocciadoro capolinea Bus n. 7</t>
+          <t>BONDO, Via Indipendenza, 105</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC TRENTO 3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CARISOLO, Scuola Primaria di Carisolo, via G. Verdi, 18/B</t>
+          <t>TRENTO, Fermata Arcate Gocciadoro capolinea Bus n. 7</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC VEZZANO</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CAVEDINE, Fermata autobus, Piazza Italia</t>
+          <t>CARISOLO, Scuola Primaria di Carisolo, via G. Verdi, 18/B</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>IC VEZZANO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CAVEDINE, Fermata autobus, Piazza Italia</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>IC VILLA LAGARINA</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>POMAROLO, Via San Cristoforo, 3 (davanti alla Chiesa)</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C19" t="n">
         <v>25</v>
       </c>
     </row>

--- a/tests/realSuite/Piano-Viaggi_Gioco-Volley_8-gennaio-2026_4-DEF_con-vettore-ed-integrazione/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_Gioco-Volley_8-gennaio-2026_4-DEF_con-vettore-ed-integrazione/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,12 +436,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IC ALTA VAL DI SOLE</t>
+          <t>IC BORGO VALSUGANA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OSSANA, Via S Michele, 11</t>
+          <t>Ist. "Rita Levi Montalcini", Via Temanza 13/c – Borgo Valsugana</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -451,76 +451,76 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC BORGO VALSUGANA</t>
+          <t>IC CHIESE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ist. "Rita Levi Montalcini", Via Temanza 13/c – Borgo Valsugana</t>
+          <t>PIEVE DI BONO-PREZZO, Via Fiera - Creto - Pieve di Bono, 1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC CHIESE</t>
+          <t>IC CIVEZZANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PIEVE DI BONO-PREZZO, Via Fiera - Creto - Pieve di Bono, 1</t>
+          <t>FORNACE, via dei Mori 2 - Fermata bus</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC CIVEZZANO</t>
+          <t>IC CLES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FORNACE, via dei Mori 2 - Fermata bus</t>
+          <t>CLES, Piazza Fiera</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC CLES</t>
+          <t>IC DRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CLES, Piazza Fiera</t>
+          <t>SP DRO, Piazza della Repubblica n.1</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC DRO</t>
+          <t>IC GIUDICARIE ESTERIORI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SP DRO, Piazza della Repubblica n.1</t>
+          <t>FIAVE', Via De Gasperi 23</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -531,37 +531,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FIAVE', Via De Gasperi 23</t>
+          <t>STENICO, Via Risorgimento 11/A</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC GIUDICARIE ESTERIORI</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>STENICO, Via Risorgimento 11/A</t>
+          <t>MEZZOLOMBARDO, via S. Francesco di fronte fermata Stazione FS</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC RIVA 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MEZZOLOMBARDO, via S. Francesco di fronte fermata Stazione FS</t>
+          <t>NAGO, Via di Tezze 4 - fermata bus</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -571,135 +571,120 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC RIVA 1</t>
+          <t>IC RIVA 2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NAGO, Via di Tezze 4 - fermata bus</t>
+          <t>RIVA DEL GARDA, Via Grez 7/F (Plesso Primaria Zadra)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC RIVA 2</t>
+          <t>IC ROVERETO NORD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RIVA DEL GARDA, Via Grez 7/F (Plesso Primaria Zadra)</t>
+          <t>ROVERETO, Fermata Bus Viale Trento, bivio Brione</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC ROVERETO NORD</t>
+          <t>IC TAIO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ROVERETO, Fermata Bus Viale Trento, bivio Brione</t>
+          <t>TRES, Scuola Primaria</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC TAIO</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TRES, Scuola Primaria</t>
+          <t>BONDO, Via Indipendenza, 105</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IC TRENTO 3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BONDO, Via Indipendenza, 105</t>
+          <t>TRENTO, Fermata Arcate Gocciadoro capolinea Bus n. 7</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC TRENTO 3</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TRENTO, Fermata Arcate Gocciadoro capolinea Bus n. 7</t>
+          <t>CARISOLO, Scuola Primaria di Carisolo, via G. Verdi, 18/B</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC VEZZANO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CARISOLO, Scuola Primaria di Carisolo, via G. Verdi, 18/B</t>
+          <t>CAVEDINE, Fermata autobus, Piazza Italia</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC VEZZANO</t>
+          <t>IC VILLA LAGARINA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CAVEDINE, Fermata autobus, Piazza Italia</t>
+          <t>POMAROLO, Via San Cristoforo, 3 (davanti alla Chiesa)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>IC VILLA LAGARINA</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>POMAROLO, Via San Cristoforo, 3 (davanti alla Chiesa)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
         <v>25</v>
       </c>
     </row>
